--- a/SLK1_combiner.xlsx
+++ b/SLK1_combiner.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="4">
   <si>
     <t>ROW</t>
   </si>
@@ -20,6 +20,9 @@
   </si>
   <si>
     <t>TERULET</t>
+  </si>
+  <si>
+    <t>SLK1</t>
   </si>
 </sst>
 </file>
@@ -57,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -68,6 +71,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -311,7 +317,9 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="F2" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
@@ -321,7 +329,9 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
@@ -331,7 +341,9 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
@@ -341,7 +353,9 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
@@ -351,7 +365,9 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
@@ -361,7 +377,9 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
@@ -371,7 +389,9 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
@@ -381,7 +401,9 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
@@ -391,7 +413,9 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
@@ -401,7 +425,9 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
@@ -411,7 +437,9 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
@@ -421,7 +449,9 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
@@ -431,7 +461,9 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="F14" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
@@ -441,7 +473,9 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="F15" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
@@ -451,7 +485,9 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="F16" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
@@ -461,7 +497,9 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="F17" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
@@ -471,7 +509,9 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="F18" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
@@ -481,7 +521,9 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="F19" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
@@ -491,7 +533,9 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="F20" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
@@ -501,7 +545,9 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="F21" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
@@ -511,7 +557,9 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="F22" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
@@ -521,7 +569,9 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
@@ -531,7 +581,9 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
@@ -541,7 +593,9 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
@@ -551,7 +605,9 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="F26" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
@@ -561,7 +617,9 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+      <c r="F27" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
@@ -571,7 +629,9 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="F28" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
@@ -581,7 +641,9 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="F29" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
@@ -591,7 +653,9 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="F30" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
@@ -601,7 +665,9 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="F31" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
@@ -611,7 +677,9 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="F32" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
@@ -621,7 +689,9 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="F33" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
@@ -631,7 +701,9 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="F34" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
@@ -641,7 +713,9 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="F35" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
@@ -651,7 +725,9 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="F36" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
@@ -661,7 +737,9 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
@@ -671,7 +749,9 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="F38" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
@@ -681,7 +761,9 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
@@ -691,7 +773,9 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="F40" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
@@ -701,7 +785,9 @@
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="F41" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
@@ -711,7 +797,9 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="F42" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
@@ -721,7 +809,9 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
@@ -731,7 +821,9 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+      <c r="F44" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
@@ -741,7 +833,9 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
+      <c r="F45" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
@@ -751,7 +845,9 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+      <c r="F46" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
@@ -761,7 +857,9 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
+      <c r="F47" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
@@ -771,7 +869,9 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
+      <c r="F48" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
@@ -781,7 +881,9 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="F49" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
@@ -791,7 +893,9 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
+      <c r="F50" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
@@ -801,7 +905,9 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
@@ -811,7 +917,9 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
+      <c r="F52" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
@@ -821,7 +929,9 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
+      <c r="F53" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
@@ -831,7 +941,9 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
+      <c r="F54" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
@@ -841,7 +953,9 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
+      <c r="F55" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
@@ -851,7 +965,9 @@
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
+      <c r="F56" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
     </row>
@@ -861,7 +977,9 @@
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
+      <c r="F57" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
     </row>
@@ -871,7 +989,9 @@
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
+      <c r="F58" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
@@ -881,7 +1001,9 @@
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
+      <c r="F59" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
     </row>
@@ -891,7 +1013,9 @@
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
+      <c r="F60" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
     </row>
@@ -901,7 +1025,9 @@
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
+      <c r="F61" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
     </row>
@@ -911,7 +1037,9 @@
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
+      <c r="F62" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
     </row>
@@ -921,7 +1049,9 @@
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
+      <c r="F63" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
     </row>
@@ -931,7 +1061,9 @@
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="F64" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
     </row>
@@ -941,7 +1073,9 @@
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
+      <c r="F65" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
     </row>
@@ -951,7 +1085,9 @@
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
     </row>
@@ -961,7 +1097,9 @@
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="F67" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
     </row>
@@ -971,7 +1109,9 @@
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
+      <c r="F68" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
@@ -981,7 +1121,9 @@
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
+      <c r="F69" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
     </row>
@@ -991,7 +1133,9 @@
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
+      <c r="F70" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
     </row>
@@ -1001,7 +1145,9 @@
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
+      <c r="F71" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
     </row>
@@ -1011,7 +1157,9 @@
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
+      <c r="F72" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
     </row>
@@ -1021,7 +1169,9 @@
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
+      <c r="F73" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
     </row>
@@ -1031,7 +1181,9 @@
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
+      <c r="F74" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
     </row>
@@ -1041,7 +1193,9 @@
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
+      <c r="F75" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
     </row>
@@ -1051,7 +1205,9 @@
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
+      <c r="F76" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
     </row>
@@ -1061,7 +1217,9 @@
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
+      <c r="F77" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
     </row>
@@ -1071,7 +1229,9 @@
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
+      <c r="F78" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
     </row>
@@ -1081,7 +1241,9 @@
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
+      <c r="F79" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
     </row>
@@ -1091,7 +1253,9 @@
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
+      <c r="F80" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
     </row>
@@ -1101,7 +1265,9 @@
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
+      <c r="F81" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
     </row>
@@ -1111,7 +1277,9 @@
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
+      <c r="F82" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
     </row>
@@ -1121,7 +1289,9 @@
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
+      <c r="F83" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
     </row>
@@ -1131,7 +1301,9 @@
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
+      <c r="F84" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
     </row>
@@ -1141,7 +1313,9 @@
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
+      <c r="F85" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
     </row>
@@ -1151,7 +1325,9 @@
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
+      <c r="F86" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
     </row>
@@ -1161,7 +1337,9 @@
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
+      <c r="F87" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
     </row>
@@ -1171,7 +1349,9 @@
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
+      <c r="F88" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
     </row>
@@ -1181,7 +1361,9 @@
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
+      <c r="F89" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
     </row>
@@ -1191,7 +1373,9 @@
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
+      <c r="F90" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
     </row>
@@ -1201,7 +1385,9 @@
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
+      <c r="F91" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
     </row>
@@ -1211,7 +1397,9 @@
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
+      <c r="F92" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
     </row>
@@ -1221,7 +1409,9 @@
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
+      <c r="F93" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
     </row>
@@ -1231,7 +1421,9 @@
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
+      <c r="F94" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
@@ -1241,7 +1433,9 @@
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
+      <c r="F95" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
     </row>
@@ -1251,7 +1445,9 @@
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
+      <c r="F96" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
     </row>
@@ -1261,7 +1457,9 @@
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
+      <c r="F97" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
     </row>
@@ -1271,7 +1469,9 @@
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
+      <c r="F98" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
     </row>
@@ -1281,7 +1481,9 @@
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
+      <c r="F99" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
     </row>
@@ -1291,7 +1493,9 @@
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
+      <c r="F100" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
     </row>
@@ -1301,7 +1505,9 @@
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
+      <c r="F101" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
     </row>
@@ -1311,7 +1517,9 @@
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
+      <c r="F102" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
     </row>
@@ -1321,7 +1529,9 @@
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
+      <c r="F103" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
     </row>
@@ -1331,7 +1541,9 @@
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
+      <c r="F104" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
     </row>
@@ -1341,7 +1553,9 @@
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
+      <c r="F105" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
     </row>
@@ -1351,7 +1565,9 @@
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
+      <c r="F106" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
     </row>
@@ -1361,7 +1577,9 @@
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
+      <c r="F107" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
     </row>
@@ -1371,7 +1589,9 @@
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
+      <c r="F108" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
     </row>
@@ -1381,7 +1601,9 @@
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
+      <c r="F109" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
     </row>
@@ -1391,7 +1613,9 @@
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
+      <c r="F110" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
     </row>
@@ -1401,7 +1625,9 @@
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
+      <c r="F111" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
     </row>
@@ -1411,7 +1637,9 @@
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
+      <c r="F112" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
     </row>
@@ -1421,7 +1649,9 @@
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
+      <c r="F113" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
     </row>
@@ -1431,7 +1661,9 @@
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
+      <c r="F114" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G114" s="3"/>
       <c r="H114" s="3"/>
     </row>
@@ -1441,7 +1673,9 @@
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
+      <c r="F115" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
     </row>
@@ -1451,7 +1685,9 @@
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
+      <c r="F116" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
     </row>
@@ -1461,7 +1697,9 @@
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
+      <c r="F117" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
     </row>
@@ -1471,7 +1709,9 @@
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
+      <c r="F118" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
     </row>
@@ -1481,7 +1721,9 @@
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
+      <c r="F119" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
     </row>
@@ -1491,7 +1733,9 @@
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
+      <c r="F120" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
     </row>
@@ -1501,7 +1745,9 @@
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
+      <c r="F121" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3"/>
     </row>
@@ -1511,7 +1757,9 @@
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
+      <c r="F122" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
     </row>
@@ -1521,7 +1769,9 @@
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
-      <c r="F123" s="3"/>
+      <c r="F123" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G123" s="3"/>
       <c r="H123" s="3"/>
     </row>
@@ -1531,7 +1781,9 @@
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
+      <c r="F124" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G124" s="3"/>
       <c r="H124" s="3"/>
     </row>
@@ -1541,7 +1793,9 @@
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
+      <c r="F125" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
     </row>
@@ -1551,7 +1805,9 @@
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
+      <c r="F126" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
     </row>
@@ -1561,7 +1817,9 @@
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
+      <c r="F127" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G127" s="3"/>
       <c r="H127" s="3"/>
     </row>
@@ -1571,7 +1829,9 @@
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
-      <c r="F128" s="3"/>
+      <c r="F128" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G128" s="3"/>
       <c r="H128" s="3"/>
     </row>
@@ -1581,7 +1841,9 @@
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
+      <c r="F129" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G129" s="3"/>
       <c r="H129" s="3"/>
     </row>
@@ -1591,7 +1853,9 @@
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
-      <c r="F130" s="3"/>
+      <c r="F130" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G130" s="3"/>
       <c r="H130" s="3"/>
     </row>
@@ -1601,7 +1865,9 @@
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
+      <c r="F131" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G131" s="3"/>
       <c r="H131" s="3"/>
     </row>
@@ -1611,7 +1877,9 @@
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
+      <c r="F132" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
     </row>
@@ -1621,7 +1889,9 @@
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
+      <c r="F133" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G133" s="3"/>
       <c r="H133" s="3"/>
     </row>
@@ -1631,7 +1901,9 @@
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
+      <c r="F134" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G134" s="3"/>
       <c r="H134" s="3"/>
     </row>
@@ -1641,7 +1913,9 @@
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
+      <c r="F135" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G135" s="3"/>
       <c r="H135" s="3"/>
     </row>
@@ -1651,7 +1925,9 @@
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
-      <c r="F136" s="3"/>
+      <c r="F136" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G136" s="3"/>
       <c r="H136" s="3"/>
     </row>
@@ -1661,7 +1937,9 @@
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
-      <c r="F137" s="3"/>
+      <c r="F137" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G137" s="3"/>
       <c r="H137" s="3"/>
     </row>
@@ -1671,7 +1949,9 @@
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
-      <c r="F138" s="3"/>
+      <c r="F138" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G138" s="3"/>
       <c r="H138" s="3"/>
     </row>
@@ -1681,7 +1961,9 @@
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
-      <c r="F139" s="3"/>
+      <c r="F139" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G139" s="3"/>
       <c r="H139" s="3"/>
     </row>
@@ -1691,7 +1973,9 @@
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
-      <c r="F140" s="3"/>
+      <c r="F140" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G140" s="3"/>
       <c r="H140" s="3"/>
     </row>
@@ -1701,7 +1985,9 @@
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
-      <c r="F141" s="3"/>
+      <c r="F141" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G141" s="3"/>
       <c r="H141" s="3"/>
     </row>
@@ -1711,7 +1997,9 @@
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
-      <c r="F142" s="3"/>
+      <c r="F142" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G142" s="3"/>
       <c r="H142" s="3"/>
     </row>
@@ -1721,7 +2009,9 @@
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
-      <c r="F143" s="3"/>
+      <c r="F143" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G143" s="3"/>
       <c r="H143" s="3"/>
     </row>
@@ -1731,7 +2021,9 @@
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
-      <c r="F144" s="3"/>
+      <c r="F144" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G144" s="3"/>
       <c r="H144" s="3"/>
     </row>
@@ -1741,7 +2033,9 @@
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
-      <c r="F145" s="3"/>
+      <c r="F145" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G145" s="3"/>
       <c r="H145" s="3"/>
     </row>
@@ -1751,7 +2045,9 @@
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
-      <c r="F146" s="3"/>
+      <c r="F146" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G146" s="3"/>
       <c r="H146" s="3"/>
     </row>
@@ -1761,7 +2057,9 @@
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
-      <c r="F147" s="3"/>
+      <c r="F147" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G147" s="3"/>
       <c r="H147" s="3"/>
     </row>
@@ -1771,7 +2069,9 @@
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
-      <c r="F148" s="3"/>
+      <c r="F148" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G148" s="3"/>
       <c r="H148" s="3"/>
     </row>
@@ -1781,7 +2081,9 @@
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
-      <c r="F149" s="3"/>
+      <c r="F149" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G149" s="3"/>
       <c r="H149" s="3"/>
     </row>
@@ -1791,7 +2093,9 @@
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
-      <c r="F150" s="3"/>
+      <c r="F150" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G150" s="3"/>
       <c r="H150" s="3"/>
     </row>
@@ -1801,7 +2105,9 @@
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
-      <c r="F151" s="3"/>
+      <c r="F151" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G151" s="3"/>
       <c r="H151" s="3"/>
     </row>
@@ -1811,7 +2117,9 @@
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
-      <c r="F152" s="3"/>
+      <c r="F152" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G152" s="3"/>
       <c r="H152" s="3"/>
     </row>
@@ -1821,7 +2129,9 @@
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
-      <c r="F153" s="3"/>
+      <c r="F153" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G153" s="3"/>
       <c r="H153" s="3"/>
     </row>
@@ -1831,7 +2141,9 @@
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
-      <c r="F154" s="3"/>
+      <c r="F154" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G154" s="3"/>
       <c r="H154" s="3"/>
     </row>
@@ -1841,7 +2153,9 @@
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
-      <c r="F155" s="3"/>
+      <c r="F155" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G155" s="3"/>
       <c r="H155" s="3"/>
     </row>
@@ -1851,7 +2165,9 @@
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
-      <c r="F156" s="3"/>
+      <c r="F156" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
     </row>
@@ -1861,7 +2177,9 @@
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
-      <c r="F157" s="3"/>
+      <c r="F157" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G157" s="3"/>
       <c r="H157" s="3"/>
     </row>
@@ -1871,7 +2189,9 @@
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
-      <c r="F158" s="3"/>
+      <c r="F158" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G158" s="3"/>
       <c r="H158" s="3"/>
     </row>
@@ -1881,7 +2201,9 @@
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
-      <c r="F159" s="3"/>
+      <c r="F159" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G159" s="3"/>
       <c r="H159" s="3"/>
     </row>
@@ -1891,7 +2213,9 @@
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
-      <c r="F160" s="3"/>
+      <c r="F160" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G160" s="3"/>
       <c r="H160" s="3"/>
     </row>
@@ -1901,7 +2225,9 @@
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
-      <c r="F161" s="3"/>
+      <c r="F161" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G161" s="3"/>
       <c r="H161" s="3"/>
     </row>
@@ -1911,7 +2237,9 @@
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
-      <c r="F162" s="3"/>
+      <c r="F162" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G162" s="3"/>
       <c r="H162" s="3"/>
     </row>
@@ -1921,7 +2249,9 @@
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
-      <c r="F163" s="3"/>
+      <c r="F163" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G163" s="3"/>
       <c r="H163" s="3"/>
     </row>
